--- a/cables.xlsx
+++ b/cables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9CF204-C7F9-F64D-92A0-67E085CA71B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D942EF-CA8C-0A4E-9CD2-7145D7722164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="760" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11772" uniqueCount="3446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11844" uniqueCount="3474">
   <si>
     <t>Tag</t>
   </si>
@@ -10382,6 +10382,90 @@
   </si>
   <si>
     <t>Christie 44339</t>
+  </si>
+  <si>
+    <t>2609-1001</t>
+  </si>
+  <si>
+    <t>2609-1002</t>
+  </si>
+  <si>
+    <t>2609-1003</t>
+  </si>
+  <si>
+    <t>2609-1004</t>
+  </si>
+  <si>
+    <t>2609-1005</t>
+  </si>
+  <si>
+    <t>2609-1006</t>
+  </si>
+  <si>
+    <t>Balcony crawlspace</t>
+  </si>
+  <si>
+    <t>Camera 1</t>
+  </si>
+  <si>
+    <t>Camera 2</t>
+  </si>
+  <si>
+    <t>Camera 3</t>
+  </si>
+  <si>
+    <t>violet</t>
+  </si>
+  <si>
+    <t>Camera Controller</t>
+  </si>
+  <si>
+    <t>Liight Console</t>
+  </si>
+  <si>
+    <t>(Future) NDI to GrandMA</t>
+  </si>
+  <si>
+    <t>46m</t>
+  </si>
+  <si>
+    <t>23m</t>
+  </si>
+  <si>
+    <t>17m</t>
+  </si>
+  <si>
+    <t>Provo #CS934</t>
+  </si>
+  <si>
+    <t>ZVHU-0002-13</t>
+  </si>
+  <si>
+    <t>blue stripe on connector</t>
+  </si>
+  <si>
+    <t>2609-1800</t>
+  </si>
+  <si>
+    <t>2609-1800-int</t>
+  </si>
+  <si>
+    <t>rear desk orange</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>hardwired</t>
+  </si>
+  <si>
+    <t>nema15p-hardwired</t>
+  </si>
+  <si>
+    <t>UPS power in</t>
+  </si>
+  <si>
+    <t>AVLI unknown</t>
   </si>
 </sst>
 </file>
@@ -19897,69 +19981,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -20193,6 +20214,69 @@
     </i>
     <i>
       <x v="53"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -20548,7 +20632,7 @@
     <col min="9" max="9" width="5.33203125" customWidth="1"/>
     <col min="10" max="10" width="19.5" customWidth="1"/>
     <col min="11" max="11" width="23.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" customWidth="1"/>
     <col min="13" max="13" width="7" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22331,7 +22415,9 @@
       <c r="A58" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="22"/>
+      <c r="B58" s="22" t="s">
+        <v>415</v>
+      </c>
       <c r="C58" s="23"/>
       <c r="D58" s="22"/>
       <c r="E58" s="23"/>
@@ -22350,7 +22436,9 @@
       <c r="J58" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="K58" s="23"/>
+      <c r="K58" s="23" t="s">
+        <v>3465</v>
+      </c>
       <c r="L58" s="23"/>
       <c r="M58" s="24"/>
     </row>
@@ -66533,108 +66621,248 @@
       <c r="M1437" s="29"/>
     </row>
     <row r="1438" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1438" s="29"/>
-      <c r="B1438" s="100"/>
+      <c r="A1438" s="29" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B1438" s="100" t="s">
+        <v>1537</v>
+      </c>
       <c r="C1438" s="83"/>
-      <c r="D1438" s="85"/>
-      <c r="E1438" s="83"/>
-      <c r="F1438" s="31"/>
+      <c r="D1438" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1438" s="83" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F1438" s="31" t="s">
+        <v>228</v>
+      </c>
       <c r="G1438" s="31"/>
-      <c r="H1438" s="29"/>
-      <c r="I1438" s="119"/>
-      <c r="J1438" s="29"/>
-      <c r="K1438" s="29"/>
-      <c r="L1438" s="31"/>
-      <c r="M1438" s="29"/>
+      <c r="H1438" s="29" t="s">
+        <v>3460</v>
+      </c>
+      <c r="I1438" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1438" s="29" t="s">
+        <v>3453</v>
+      </c>
+      <c r="K1438" s="29" t="s">
+        <v>3456</v>
+      </c>
+      <c r="L1438" s="31" t="s">
+        <v>3463</v>
+      </c>
+      <c r="M1438" s="29" t="s">
+        <v>3452</v>
+      </c>
     </row>
     <row r="1439" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1439" s="29"/>
-      <c r="B1439" s="100"/>
+      <c r="A1439" s="29" t="s">
+        <v>3447</v>
+      </c>
+      <c r="B1439" s="100" t="s">
+        <v>1537</v>
+      </c>
       <c r="C1439" s="83"/>
-      <c r="D1439" s="85"/>
-      <c r="E1439" s="83"/>
-      <c r="F1439" s="31"/>
+      <c r="D1439" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1439" s="83" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F1439" s="31" t="s">
+        <v>228</v>
+      </c>
       <c r="G1439" s="31"/>
-      <c r="H1439" s="29"/>
-      <c r="I1439" s="119"/>
-      <c r="J1439" s="29"/>
-      <c r="K1439" s="29"/>
-      <c r="L1439" s="31"/>
+      <c r="H1439" s="29" t="s">
+        <v>3461</v>
+      </c>
+      <c r="I1439" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1439" s="29" t="s">
+        <v>3454</v>
+      </c>
+      <c r="K1439" s="29" t="s">
+        <v>3456</v>
+      </c>
+      <c r="L1439" s="31" t="s">
+        <v>3463</v>
+      </c>
       <c r="M1439" s="29"/>
     </row>
     <row r="1440" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1440" s="29"/>
-      <c r="B1440" s="100"/>
+      <c r="A1440" s="29" t="s">
+        <v>3448</v>
+      </c>
+      <c r="B1440" s="100" t="s">
+        <v>1537</v>
+      </c>
       <c r="C1440" s="83"/>
-      <c r="D1440" s="85"/>
-      <c r="E1440" s="83"/>
-      <c r="F1440" s="31"/>
+      <c r="D1440" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1440" s="83" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F1440" s="31" t="s">
+        <v>228</v>
+      </c>
       <c r="G1440" s="31"/>
-      <c r="H1440" s="29"/>
-      <c r="I1440" s="119"/>
-      <c r="J1440" s="29"/>
-      <c r="K1440" s="29"/>
-      <c r="L1440" s="31"/>
+      <c r="H1440" s="29" t="s">
+        <v>3462</v>
+      </c>
+      <c r="I1440" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1440" s="29" t="s">
+        <v>3455</v>
+      </c>
+      <c r="K1440" s="29" t="s">
+        <v>3456</v>
+      </c>
+      <c r="L1440" s="31" t="s">
+        <v>3463</v>
+      </c>
       <c r="M1440" s="29"/>
     </row>
     <row r="1441" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1441" s="29"/>
-      <c r="B1441" s="100"/>
+      <c r="A1441" s="29" t="s">
+        <v>3449</v>
+      </c>
+      <c r="B1441" s="100" t="s">
+        <v>1537</v>
+      </c>
       <c r="C1441" s="83"/>
-      <c r="D1441" s="85"/>
-      <c r="E1441" s="83"/>
-      <c r="F1441" s="31"/>
+      <c r="D1441" s="83" t="s">
+        <v>3464</v>
+      </c>
+      <c r="E1441" s="83" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F1441" s="31" t="s">
+        <v>228</v>
+      </c>
       <c r="G1441" s="31"/>
-      <c r="H1441" s="29"/>
-      <c r="I1441" s="119"/>
-      <c r="J1441" s="29"/>
-      <c r="K1441" s="29"/>
-      <c r="L1441" s="31"/>
+      <c r="H1441" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="I1441" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1441" s="29" t="s">
+        <v>3457</v>
+      </c>
+      <c r="K1441" s="29" t="s">
+        <v>3456</v>
+      </c>
+      <c r="L1441" s="31" t="s">
+        <v>3463</v>
+      </c>
       <c r="M1441" s="29"/>
     </row>
     <row r="1442" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1442" s="29"/>
-      <c r="B1442" s="100"/>
+      <c r="A1442" s="29" t="s">
+        <v>3450</v>
+      </c>
+      <c r="B1442" s="100" t="s">
+        <v>1537</v>
+      </c>
       <c r="C1442" s="83"/>
-      <c r="D1442" s="85"/>
+      <c r="D1442" s="83" t="s">
+        <v>3464</v>
+      </c>
       <c r="E1442" s="83"/>
-      <c r="F1442" s="31"/>
+      <c r="F1442" s="31" t="s">
+        <v>228</v>
+      </c>
       <c r="G1442" s="31"/>
-      <c r="H1442" s="29"/>
-      <c r="I1442" s="119"/>
-      <c r="J1442" s="29"/>
-      <c r="K1442" s="29"/>
-      <c r="L1442" s="31"/>
+      <c r="H1442" s="29" t="s">
+        <v>3462</v>
+      </c>
+      <c r="I1442" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1442" s="29" t="s">
+        <v>3458</v>
+      </c>
+      <c r="K1442" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="L1442" s="31" t="s">
+        <v>3463</v>
+      </c>
       <c r="M1442" s="29"/>
     </row>
     <row r="1443" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1443" s="29"/>
-      <c r="B1443" s="100"/>
+      <c r="A1443" s="29" t="s">
+        <v>3451</v>
+      </c>
+      <c r="B1443" s="100" t="s">
+        <v>1537</v>
+      </c>
       <c r="C1443" s="83"/>
-      <c r="D1443" s="85"/>
+      <c r="D1443" s="83" t="s">
+        <v>3464</v>
+      </c>
       <c r="E1443" s="83"/>
-      <c r="F1443" s="31"/>
+      <c r="F1443" s="31" t="s">
+        <v>228</v>
+      </c>
       <c r="G1443" s="31"/>
-      <c r="H1443" s="29"/>
-      <c r="I1443" s="119"/>
-      <c r="J1443" s="29"/>
-      <c r="K1443" s="29"/>
-      <c r="L1443" s="31"/>
+      <c r="H1443" s="29" t="s">
+        <v>3462</v>
+      </c>
+      <c r="I1443" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1443" s="29" t="s">
+        <v>3459</v>
+      </c>
+      <c r="K1443" s="29" t="s">
+        <v>3456</v>
+      </c>
+      <c r="L1443" s="31" t="s">
+        <v>3463</v>
+      </c>
       <c r="M1443" s="29"/>
     </row>
     <row r="1444" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1444" s="29"/>
-      <c r="B1444" s="100"/>
-      <c r="C1444" s="83"/>
-      <c r="D1444" s="85"/>
-      <c r="E1444" s="83"/>
-      <c r="F1444" s="31"/>
-      <c r="G1444" s="31"/>
-      <c r="H1444" s="29"/>
-      <c r="I1444" s="119"/>
-      <c r="J1444" s="29"/>
+      <c r="A1444" s="29" t="s">
+        <v>3467</v>
+      </c>
+      <c r="B1444" s="100" t="s">
+        <v>3468</v>
+      </c>
+      <c r="C1444" s="83" t="s">
+        <v>3469</v>
+      </c>
+      <c r="D1444" s="85" t="s">
+        <v>3466</v>
+      </c>
+      <c r="E1444" s="83" t="s">
+        <v>3470</v>
+      </c>
+      <c r="F1444" s="31" t="s">
+        <v>3471</v>
+      </c>
+      <c r="G1444" s="31" t="s">
+        <v>3415</v>
+      </c>
+      <c r="H1444" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1444" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1444" s="29" t="s">
+        <v>3472</v>
+      </c>
       <c r="K1444" s="29"/>
-      <c r="L1444" s="31"/>
+      <c r="L1444" s="31" t="s">
+        <v>3473</v>
+      </c>
       <c r="M1444" s="29"/>
     </row>
     <row r="1445" spans="1:13" x14ac:dyDescent="0.2">

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D942EF-CA8C-0A4E-9CD2-7145D7722164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA4FA30-4F37-8D49-A581-B1E07FAD6101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="760" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11844" uniqueCount="3474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11853" uniqueCount="3476">
   <si>
     <t>Tag</t>
   </si>
@@ -10466,6 +10466,12 @@
   </si>
   <si>
     <t>AVLI unknown</t>
+  </si>
+  <si>
+    <t>2602-1800-F36</t>
+  </si>
+  <si>
+    <t>notag1445</t>
   </si>
 </sst>
 </file>
@@ -66625,9 +66631,11 @@
         <v>3446</v>
       </c>
       <c r="B1438" s="100" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C1438" s="83"/>
+        <v>3474</v>
+      </c>
+      <c r="C1438" s="83" t="s">
+        <v>2344</v>
+      </c>
       <c r="D1438" s="83" t="s">
         <v>65</v>
       </c>
@@ -66662,9 +66670,11 @@
         <v>3447</v>
       </c>
       <c r="B1439" s="100" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C1439" s="83"/>
+        <v>3474</v>
+      </c>
+      <c r="C1439" s="83" t="s">
+        <v>2345</v>
+      </c>
       <c r="D1439" s="83" t="s">
         <v>65</v>
       </c>
@@ -66697,9 +66707,11 @@
         <v>3448</v>
       </c>
       <c r="B1440" s="100" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C1440" s="83"/>
+        <v>3474</v>
+      </c>
+      <c r="C1440" s="83" t="s">
+        <v>2346</v>
+      </c>
       <c r="D1440" s="83" t="s">
         <v>65</v>
       </c>
@@ -66732,9 +66744,11 @@
         <v>3449</v>
       </c>
       <c r="B1441" s="100" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C1441" s="83"/>
+        <v>3474</v>
+      </c>
+      <c r="C1441" s="83" t="s">
+        <v>1818</v>
+      </c>
       <c r="D1441" s="83" t="s">
         <v>3464</v>
       </c>
@@ -66767,9 +66781,11 @@
         <v>3450</v>
       </c>
       <c r="B1442" s="100" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C1442" s="83"/>
+        <v>3474</v>
+      </c>
+      <c r="C1442" s="83" t="s">
+        <v>2365</v>
+      </c>
       <c r="D1442" s="83" t="s">
         <v>3464</v>
       </c>
@@ -66800,7 +66816,7 @@
         <v>3451</v>
       </c>
       <c r="B1443" s="100" t="s">
-        <v>1537</v>
+        <v>3474</v>
       </c>
       <c r="C1443" s="83"/>
       <c r="D1443" s="83" t="s">
@@ -66866,11 +66882,19 @@
       <c r="M1444" s="29"/>
     </row>
     <row r="1445" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1445" s="29"/>
-      <c r="B1445" s="100"/>
+      <c r="A1445" s="29" t="s">
+        <v>3475</v>
+      </c>
+      <c r="B1445" s="100" t="s">
+        <v>1640</v>
+      </c>
       <c r="C1445" s="83"/>
-      <c r="D1445" s="85"/>
-      <c r="E1445" s="83"/>
+      <c r="D1445" s="100" t="s">
+        <v>3474</v>
+      </c>
+      <c r="E1445" s="83" t="s">
+        <v>2358</v>
+      </c>
       <c r="F1445" s="31"/>
       <c r="G1445" s="31"/>
       <c r="H1445" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA4FA30-4F37-8D49-A581-B1E07FAD6101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F406B7C7-A91A-A144-A455-3CD07914E9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="760" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -16,10 +16,10 @@
     <sheet name="Cables" sheetId="1" r:id="rId1"/>
     <sheet name="Summary" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
-    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="3" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11853" uniqueCount="3476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11873" uniqueCount="3483">
   <si>
     <t>Tag</t>
   </si>
@@ -10472,6 +10472,27 @@
   </si>
   <si>
     <t>notag1445</t>
+  </si>
+  <si>
+    <t>2610-0201</t>
+  </si>
+  <si>
+    <t>2610-0200</t>
+  </si>
+  <si>
+    <t>sACN for Stage</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>in rack</t>
+  </si>
+  <si>
+    <t>rt1447</t>
+  </si>
+  <si>
+    <t>sACN</t>
   </si>
 </sst>
 </file>
@@ -19987,7 +20008,70 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -20220,69 +20304,6 @@
     </i>
     <i>
       <x v="53"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -66905,31 +66926,71 @@
       <c r="M1445" s="29"/>
     </row>
     <row r="1446" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1446" s="29"/>
-      <c r="B1446" s="100"/>
-      <c r="C1446" s="83"/>
-      <c r="D1446" s="85"/>
-      <c r="E1446" s="83"/>
-      <c r="F1446" s="31"/>
-      <c r="G1446" s="31"/>
-      <c r="H1446" s="29"/>
-      <c r="I1446" s="119"/>
-      <c r="J1446" s="29"/>
-      <c r="K1446" s="29"/>
-      <c r="L1446" s="31"/>
-      <c r="M1446" s="29"/>
+      <c r="A1446" s="29" t="s">
+        <v>3476</v>
+      </c>
+      <c r="B1446" s="100" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C1446" s="83" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D1446" s="85" t="s">
+        <v>3477</v>
+      </c>
+      <c r="E1446" s="83" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F1446" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="G1446" s="31" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H1446" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1446" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1446" s="29" t="s">
+        <v>3478</v>
+      </c>
+      <c r="K1446" s="29" t="s">
+        <v>3479</v>
+      </c>
+      <c r="L1446" s="31" t="s">
+        <v>3463</v>
+      </c>
+      <c r="M1446" s="29" t="s">
+        <v>3480</v>
+      </c>
     </row>
     <row r="1447" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1447" s="29"/>
-      <c r="B1447" s="100"/>
+      <c r="A1447" s="29" t="s">
+        <v>3481</v>
+      </c>
+      <c r="B1447" s="101" t="s">
+        <v>3419</v>
+      </c>
       <c r="C1447" s="83"/>
-      <c r="D1447" s="85"/>
+      <c r="D1447" s="85" t="s">
+        <v>3477</v>
+      </c>
       <c r="E1447" s="83"/>
-      <c r="F1447" s="31"/>
-      <c r="G1447" s="31"/>
+      <c r="F1447" s="31" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G1447" s="31" t="s">
+        <v>3482</v>
+      </c>
       <c r="H1447" s="29"/>
-      <c r="I1447" s="119"/>
-      <c r="J1447" s="29"/>
+      <c r="I1447" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="J1447" s="29" t="s">
+        <v>3478</v>
+      </c>
       <c r="K1447" s="29"/>
       <c r="L1447" s="31"/>
       <c r="M1447" s="29"/>
